--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,11 +817,11 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105104</v>
+        <v>105450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105450</v>
+        <v>105553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105553</v>
+        <v>105561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105561</v>
+        <v>105563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105563</v>
+        <v>105571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>119257593</v>
       </c>
       <c r="B3" t="n">
-        <v>105571</v>
+        <v>105574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,133 +807,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>119257593</v>
-      </c>
-      <c r="B3" t="n">
-        <v>105574</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>673</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Backmåra</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Galium suecicum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Sterner) Ehrend.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Håkantorpet, 650 m SSV , Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>467060</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6255256</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Osby</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Örkened</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>M-Osb-0221</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Blommar ännu.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>86360841</v>
       </c>
       <c r="B2" t="n">
-        <v>103365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467059.8040485294</v>
+        <v>467060</v>
       </c>
       <c r="R2" t="n">
-        <v>6255255.566334734</v>
+        <v>6255256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,19 +760,9 @@
           <t>2020-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86360841</v>
       </c>
       <c r="B2" t="n">
-        <v>105473</v>
+        <v>105486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86360841</v>
       </c>
       <c r="B2" t="n">
-        <v>105486</v>
+        <v>105489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50573-2019 artfynd.xlsx
+++ b/artfynd/A 50573-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86360841</v>
       </c>
       <c r="B2" t="n">
-        <v>105489</v>
+        <v>105498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
